--- a/output/roomself_excel/483.xlsx
+++ b/output/roomself_excel/483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>127390</v>
+        <v>77760</v>
       </c>
       <c r="D2" t="n">
-        <v>4532</v>
+        <v>2232</v>
       </c>
       <c r="E2" t="n">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>688769</v>
+        <v>335614</v>
       </c>
       <c r="D3" t="n">
-        <v>11812</v>
+        <v>5164</v>
       </c>
       <c r="E3" t="n">
-        <v>1059</v>
+        <v>929</v>
       </c>
       <c r="F3" t="n">
-        <v>929</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>109582</v>
+        <v>136416</v>
       </c>
       <c r="D4" t="n">
-        <v>2668</v>
+        <v>3148</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="F4" t="n">
-        <v>318</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>136416</v>
+        <v>76680</v>
       </c>
       <c r="D5" t="n">
-        <v>3148</v>
+        <v>2216</v>
       </c>
       <c r="E5" t="n">
-        <v>505</v>
+        <v>284</v>
       </c>
       <c r="F5" t="n">
-        <v>424</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
         <v>401</v>
       </c>
       <c r="F7" t="n">
-        <v>382</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         <v>411</v>
       </c>
       <c r="F8" t="n">
-        <v>381</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49720</v>
+        <v>53253</v>
       </c>
       <c r="D9" t="n">
-        <v>1784</v>
+        <v>1896</v>
       </c>
       <c r="E9" t="n">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>211639</v>
+        <v>198715</v>
       </c>
       <c r="D10" t="n">
-        <v>4412</v>
+        <v>5124</v>
       </c>
       <c r="E10" t="n">
-        <v>790</v>
+        <v>219</v>
       </c>
       <c r="F10" t="n">
-        <v>247</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26331</v>
+        <v>26880</v>
       </c>
       <c r="D11" t="n">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="E11" t="n">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21432</v>
+        <v>26331</v>
       </c>
       <c r="D12" t="n">
-        <v>1288</v>
+        <v>1328</v>
       </c>
       <c r="E12" t="n">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>375680</v>
+        <v>21432</v>
       </c>
       <c r="D13" t="n">
-        <v>4908</v>
+        <v>1288</v>
       </c>
       <c r="E13" t="n">
-        <v>718</v>
+        <v>244</v>
       </c>
       <c r="F13" t="n">
-        <v>688</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26880</v>
+        <v>22090</v>
       </c>
       <c r="D14" t="n">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="E14" t="n">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23200</v>
+        <v>56024</v>
       </c>
       <c r="D15" t="n">
-        <v>1220</v>
+        <v>1944</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22090</v>
+        <v>15980</v>
       </c>
       <c r="D16" t="n">
-        <v>1316</v>
+        <v>1056</v>
       </c>
       <c r="E16" t="n">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>198804</v>
+        <v>178605</v>
       </c>
       <c r="D17" t="n">
-        <v>4536</v>
+        <v>3528</v>
       </c>
       <c r="E17" t="n">
-        <v>543</v>
+        <v>315</v>
       </c>
       <c r="F17" t="n">
-        <v>455</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>61312</v>
+        <v>19800</v>
       </c>
       <c r="D18" t="n">
-        <v>2820</v>
+        <v>1140</v>
       </c>
       <c r="E18" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -840,17 +840,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51554</v>
+        <v>211639</v>
       </c>
       <c r="D19" t="n">
-        <v>1884</v>
+        <v>4412</v>
       </c>
       <c r="E19" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
         <v>23</v>
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>56024</v>
+        <v>375680</v>
       </c>
       <c r="D20" t="n">
-        <v>1944</v>
+        <v>4908</v>
       </c>
       <c r="E20" t="n">
-        <v>188</v>
+        <v>688</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15980</v>
+        <v>127390</v>
       </c>
       <c r="D21" t="n">
-        <v>1056</v>
+        <v>4532</v>
       </c>
       <c r="E21" t="n">
-        <v>183</v>
+        <v>268</v>
       </c>
       <c r="F21" t="n">
-        <v>107</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>178605</v>
+        <v>109582</v>
       </c>
       <c r="D22" t="n">
-        <v>3528</v>
+        <v>2668</v>
       </c>
       <c r="E22" t="n">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>53253</v>
+        <v>49720</v>
       </c>
       <c r="D23" t="n">
-        <v>1896</v>
+        <v>1784</v>
       </c>
       <c r="E23" t="n">
-        <v>455</v>
+        <v>220</v>
       </c>
       <c r="F23" t="n">
-        <v>258</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100522</v>
+        <v>23200</v>
       </c>
       <c r="D24" t="n">
-        <v>2788</v>
+        <v>1220</v>
       </c>
       <c r="E24" t="n">
-        <v>264</v>
+        <v>145</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20790</v>
+        <v>198804</v>
       </c>
       <c r="D25" t="n">
-        <v>1164</v>
+        <v>4536</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19800</v>
+        <v>61312</v>
       </c>
       <c r="D26" t="n">
-        <v>1140</v>
+        <v>2820</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52156</v>
+        <v>51554</v>
       </c>
       <c r="D27" t="n">
-        <v>1828</v>
+        <v>1884</v>
       </c>
       <c r="E27" t="n">
-        <v>258</v>
+        <v>173</v>
       </c>
       <c r="F27" t="n">
-        <v>244</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1042,15 +1042,81 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>100522</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2788</v>
+      </c>
+      <c r="E28" t="n">
+        <v>264</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20790</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1164</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>52156</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E30" t="n">
+        <v>258</v>
+      </c>
+      <c r="F30" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>25905</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D31" t="n">
         <v>1288</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E31" t="n">
         <v>165</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F31" t="n">
         <v>22</v>
       </c>
     </row>

--- a/output/roomself_excel/483.xlsx
+++ b/output/roomself_excel/483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2232</v>
       </c>
-      <c r="E2" t="n">
-        <v>313</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>270</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>5164</v>
       </c>
-      <c r="E3" t="n">
-        <v>929</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>412</v>
-      </c>
+        <v>879</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>760</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>3148</v>
       </c>
-      <c r="E4" t="n">
-        <v>424</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>424</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>400</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>2216</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>284</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>26</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>3104</v>
       </c>
-      <c r="E6" t="n">
-        <v>504</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>401</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>399</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +707,31 @@
       <c r="D7" t="n">
         <v>3116</v>
       </c>
-      <c r="E7" t="n">
-        <v>401</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>368</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>377</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,31 @@
       <c r="D8" t="n">
         <v>3152</v>
       </c>
-      <c r="E8" t="n">
-        <v>411</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>368</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>387</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +789,23 @@
       <c r="D9" t="n">
         <v>1896</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>183</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>23</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +822,23 @@
       <c r="D10" t="n">
         <v>5124</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>219</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>25</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +855,23 @@
       <c r="D11" t="n">
         <v>1312</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>168</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>25</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +888,23 @@
       <c r="D12" t="n">
         <v>1328</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>201</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>13</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,31 @@
       <c r="D13" t="n">
         <v>1288</v>
       </c>
-      <c r="E13" t="n">
-        <v>244</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>107</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>228</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +962,23 @@
       <c r="D14" t="n">
         <v>1316</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>235</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>13</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +995,31 @@
       <c r="D15" t="n">
         <v>1944</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>188</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>23</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>298</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1036,31 @@
       <c r="D16" t="n">
         <v>1056</v>
       </c>
-      <c r="E16" t="n">
-        <v>183</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>94</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1077,31 @@
       <c r="D17" t="n">
         <v>3528</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>567</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>315</v>
       </c>
-      <c r="F17" t="n">
+      <c r="J17" t="n">
         <v>22</v>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1118,15 @@
       <c r="D18" t="n">
         <v>1140</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1143,23 @@
       <c r="D19" t="n">
         <v>4412</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>102</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>23</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1176,23 @@
       <c r="D20" t="n">
         <v>4908</v>
       </c>
-      <c r="E20" t="n">
-        <v>688</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>587</v>
-      </c>
+        <v>1174</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1209,31 @@
       <c r="D21" t="n">
         <v>4532</v>
       </c>
-      <c r="E21" t="n">
-        <v>268</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>81</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>114</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1250,31 @@
       <c r="D22" t="n">
         <v>2668</v>
       </c>
-      <c r="E22" t="n">
-        <v>400</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>318</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>293</v>
+      </c>
+      <c r="J22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1291,23 @@
       <c r="D23" t="n">
         <v>1784</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>220</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>24</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1324,23 @@
       <c r="D24" t="n">
         <v>1220</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>145</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>25</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1357,38 @@
       <c r="D25" t="n">
         <v>4536</v>
       </c>
-      <c r="E25" t="n">
-        <v>543</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>455</v>
+        <v>432</v>
+      </c>
+      <c r="G25" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>376</v>
+      </c>
+      <c r="J25" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -1003,12 +1406,23 @@
       <c r="D26" t="n">
         <v>2820</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>216</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>23</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1439,23 @@
       <c r="D27" t="n">
         <v>1884</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>173</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>23</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1472,23 @@
       <c r="D28" t="n">
         <v>2788</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>264</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>22</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1505,15 @@
       <c r="D29" t="n">
         <v>1164</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1530,31 @@
       <c r="D30" t="n">
         <v>1828</v>
       </c>
-      <c r="E30" t="n">
-        <v>258</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>244</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G30" t="n">
+        <v>23</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>221</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1571,23 @@
       <c r="D31" t="n">
         <v>1288</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>165</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>22</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
